--- a/spreadsheet_codegen/examples/abs_fpi/abs_fpi_external.xlsx
+++ b/spreadsheet_codegen/examples/abs_fpi/abs_fpi_external.xlsx
@@ -661,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -708,7 +708,7 @@
     <row r="7">
       <c r="A7" s="67" t="inlineStr">
         <is>
-          <t xml:space="preserve">          excel-codegen render -c &lt;配置&gt;.yaml -x abs_fpi_external.xlsx --write-excel</t>
+          <t xml:space="preserve">          spreadsheet-codegen render -c &lt;配置&gt;.yaml -x abs_fpi_external.xlsx --write-excel</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
     <row r="9">
       <c r="A9" s="65" t="inlineStr">
         <is>
-          <t xml:space="preserve">      想确认表里的代码是不是已经过期：excel-codegen check -c &lt;配置&gt;.yaml</t>
+          <t xml:space="preserve">      想确认表里的代码是不是已经过期：spreadsheet-codegen check -c &lt;配置&gt;.yaml</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D94"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="2" max="2"/>
@@ -2744,8 +2744,6 @@
         <v/>
       </c>
     </row>
-    <row r="93"/>
-    <row r="94"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2757,7 +2755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:X6"/>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -2785,6 +2783,7 @@
     <col width="160" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="18" t="inlineStr">
         <is>
@@ -3082,8 +3081,6 @@
         <v/>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4426,7 +4423,7 @@
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>## excel-codegen-meta</t>
+          <t>## spreadsheet-codegen-meta</t>
         </is>
       </c>
     </row>
